--- a/data_lake/industry/Automobile/US Total Vehicle Sales.xlsx
+++ b/data_lake/industry/Automobile/US Total Vehicle Sales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/Automobile/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\industry\Automobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459634F4-770F-F548-8805-C878E2D5980E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603C8C77-9A4A-4AE7-87A6-6FA7D8E74C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19380" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MIUSSAAR" sheetId="1" r:id="rId1"/>
@@ -447,19 +447,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G216"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G217"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -476,7 +476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>39479</v>
       </c>
@@ -510,7 +510,7 @@
       </c>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>39539</v>
       </c>
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>39569</v>
       </c>
@@ -563,7 +563,7 @@
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>39600</v>
       </c>
@@ -582,7 +582,7 @@
       </c>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>39722</v>
       </c>
@@ -601,7 +601,7 @@
       </c>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>39783</v>
       </c>
@@ -620,7 +620,7 @@
       </c>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>39814</v>
       </c>
@@ -639,7 +639,7 @@
       </c>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>39845</v>
       </c>
@@ -658,7 +658,7 @@
       </c>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>39873</v>
       </c>
@@ -677,7 +677,7 @@
       </c>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>39904</v>
       </c>
@@ -696,7 +696,7 @@
       </c>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>39934</v>
       </c>
@@ -715,7 +715,7 @@
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>39965</v>
       </c>
@@ -734,7 +734,7 @@
       </c>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>39995</v>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>40026</v>
       </c>
@@ -772,7 +772,7 @@
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>40057</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>40087</v>
       </c>
@@ -810,7 +810,7 @@
       </c>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>40118</v>
       </c>
@@ -829,7 +829,7 @@
       </c>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>40148</v>
       </c>
@@ -848,7 +848,7 @@
       </c>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>40179</v>
       </c>
@@ -867,7 +867,7 @@
       </c>
       <c r="G20" s="6"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>40210</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>40238</v>
       </c>
@@ -905,7 +905,7 @@
       </c>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>40269</v>
       </c>
@@ -924,7 +924,7 @@
       </c>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>40299</v>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>40330</v>
       </c>
@@ -962,7 +962,7 @@
       </c>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>40360</v>
       </c>
@@ -981,7 +981,7 @@
       </c>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>40391</v>
       </c>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>40422</v>
       </c>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>40452</v>
       </c>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>40483</v>
       </c>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>40513</v>
       </c>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>40544</v>
       </c>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="G32" s="6"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>40575</v>
       </c>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G33" s="6"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>40603</v>
       </c>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G34" s="6"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>40634</v>
       </c>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G35" s="6"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>40664</v>
       </c>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="G36" s="6"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>40695</v>
       </c>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G37" s="6"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>40725</v>
       </c>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G38" s="6"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>40756</v>
       </c>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G39" s="6"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>40787</v>
       </c>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G40" s="6"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40817</v>
       </c>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G41" s="6"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40848</v>
       </c>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G42" s="6"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>40878</v>
       </c>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>40909</v>
       </c>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G44" s="6"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>40940</v>
       </c>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G45" s="6"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>40969</v>
       </c>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G46" s="6"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>41000</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G47" s="6"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>41030</v>
       </c>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G48" s="6"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>41061</v>
       </c>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G49" s="6"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>41091</v>
       </c>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G50" s="6"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>41122</v>
       </c>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G51" s="6"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>41153</v>
       </c>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G52" s="6"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>41183</v>
       </c>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G53" s="6"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>41214</v>
       </c>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G54" s="6"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>41244</v>
       </c>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>41275</v>
       </c>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>41306</v>
       </c>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G57" s="6"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>41334</v>
       </c>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G58" s="6"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>41365</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G59" s="6"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>41395</v>
       </c>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G60" s="6"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>41426</v>
       </c>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G61" s="6"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>41456</v>
       </c>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G62" s="6"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>41487</v>
       </c>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G63" s="6"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>41518</v>
       </c>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G64" s="6"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>41548</v>
       </c>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="G65" s="6"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>41579</v>
       </c>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G66" s="6"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>41609</v>
       </c>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G67" s="6"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>41640</v>
       </c>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G68" s="6"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>41671</v>
       </c>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G69" s="6"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>41699</v>
       </c>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G70" s="6"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>41730</v>
       </c>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G71" s="6"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>41760</v>
       </c>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G72" s="6"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>41791</v>
       </c>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G73" s="6"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>41821</v>
       </c>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G74" s="6"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>41852</v>
       </c>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G75" s="6"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>41883</v>
       </c>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G76" s="6"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>41913</v>
       </c>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G77" s="6"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>41944</v>
       </c>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G78" s="6"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>41974</v>
       </c>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G79" s="6"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>42005</v>
       </c>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G80" s="6"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>42036</v>
       </c>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G81" s="6"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>42064</v>
       </c>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>42095</v>
       </c>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G83" s="6"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>42125</v>
       </c>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G84" s="6"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>42156</v>
       </c>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G85" s="6"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>42186</v>
       </c>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G86" s="6"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>42217</v>
       </c>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G87" s="6"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>42248</v>
       </c>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G88" s="6"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>42278</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G89" s="6"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>42309</v>
       </c>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="G90" s="6"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>42339</v>
       </c>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>42370</v>
       </c>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="G92" s="6"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>42401</v>
       </c>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G93" s="6"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>42430</v>
       </c>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G94" s="6"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>42461</v>
       </c>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G95" s="6"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>42491</v>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G96" s="6"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>42522</v>
       </c>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>42552</v>
       </c>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>42583</v>
       </c>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G99" s="6"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>42614</v>
       </c>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G100" s="6"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>42644</v>
       </c>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G101" s="6"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>42675</v>
       </c>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G102" s="6"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>42705</v>
       </c>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G103" s="6"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>42736</v>
       </c>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G104" s="6"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>42767</v>
       </c>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G105" s="6"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>42795</v>
       </c>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G106" s="6"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>42826</v>
       </c>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G107" s="6"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>42856</v>
       </c>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G108" s="6"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>42887</v>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G109" s="6"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>42917</v>
       </c>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G110" s="6"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>42948</v>
       </c>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G111" s="6"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>42979</v>
       </c>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G112" s="6"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>43009</v>
       </c>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G113" s="6"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>43040</v>
       </c>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="G114" s="6"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>43070</v>
       </c>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G115" s="6"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>43101</v>
       </c>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G116" s="6"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>43132</v>
       </c>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G117" s="6"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>43160</v>
       </c>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G118" s="6"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>43191</v>
       </c>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G119" s="6"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>43221</v>
       </c>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G120" s="6"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>43252</v>
       </c>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G121" s="6"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>43282</v>
       </c>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="G122" s="6"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>43313</v>
       </c>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G123" s="6"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>43344</v>
       </c>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G124" s="6"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>43374</v>
       </c>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G125" s="6"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>43405</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G126" s="6"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>43435</v>
       </c>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G127" s="6"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>43466</v>
       </c>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G128" s="6"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>43497</v>
       </c>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G129" s="6"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>43525</v>
       </c>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="G130" s="6"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>43556</v>
       </c>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="G131" s="6"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>43586</v>
       </c>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G132" s="6"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>43617</v>
       </c>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G133" s="6"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>43647</v>
       </c>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G134" s="6"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>43678</v>
       </c>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="G135" s="6"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>43709</v>
       </c>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G136" s="6"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>43739</v>
       </c>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G137" s="6"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>43770</v>
       </c>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="G138" s="6"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>43800</v>
       </c>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="G139" s="6"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>43831</v>
       </c>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G140" s="6"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>43862</v>
       </c>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="G141" s="6"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>43891</v>
       </c>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="G142" s="6"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>43922</v>
       </c>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="G143" s="6"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>43952</v>
       </c>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="G144" s="6"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>43983</v>
       </c>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G145" s="6"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>44013</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="G146" s="6"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>44044</v>
       </c>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G147" s="6"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>44075</v>
       </c>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G148" s="6"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>44105</v>
       </c>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="G149" s="6"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>44136</v>
       </c>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G150" s="6"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>44166</v>
       </c>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G151" s="6"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>44197</v>
       </c>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G152" s="6"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>44228</v>
       </c>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="G153" s="6"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>44256</v>
       </c>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="G154" s="6"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>44287</v>
       </c>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G155" s="6"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>44317</v>
       </c>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="G156" s="6"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>44348</v>
       </c>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="G157" s="6"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>44378</v>
       </c>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="G158" s="6"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>44409</v>
       </c>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="G159" s="6"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>44440</v>
       </c>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G160" s="6"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>44470</v>
       </c>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G161" s="6"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>44501</v>
       </c>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="G162" s="6"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>44531</v>
       </c>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G163" s="6"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>44562</v>
       </c>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G164" s="6"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>44593</v>
       </c>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="G165" s="6"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>44621</v>
       </c>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="G166" s="6"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>44652</v>
       </c>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G167" s="6"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>44682</v>
       </c>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="G168" s="6"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>44713</v>
       </c>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G169" s="6"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>44743</v>
       </c>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="G170" s="6"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>44774</v>
       </c>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G171" s="6"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>44805</v>
       </c>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="G172" s="6"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>44835</v>
       </c>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G173" s="6"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>44866</v>
       </c>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="G174" s="6"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>44896</v>
       </c>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G175" s="6"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>44927</v>
       </c>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G176" s="6"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>44958</v>
       </c>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="G177" s="6"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>44986</v>
       </c>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G178" s="6"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>45017</v>
       </c>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="G179" s="6"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>45047</v>
       </c>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G180" s="6"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>45078</v>
       </c>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="G181" s="6"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>45108</v>
       </c>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G182" s="6"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>45139</v>
       </c>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="G183" s="6"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>45170</v>
       </c>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G184" s="6"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>45200</v>
       </c>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="G185" s="6"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>45231</v>
       </c>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G186" s="6"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>45261</v>
       </c>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="G187" s="6"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>45292</v>
       </c>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="G188" s="6"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>45323</v>
       </c>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="G189" s="6"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>45352</v>
       </c>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="G190" s="6"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>45383</v>
       </c>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="G191" s="6"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>45413</v>
       </c>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="G192" s="6"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>45444</v>
       </c>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G193" s="6"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>45474</v>
       </c>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G194" s="6"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>45505</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D195" s="4" t="str">
-        <f t="shared" ref="D195:D216" si="3">IF(
+        <f t="shared" ref="D195:D217" si="3">IF(
  AND(
   B195 &gt;= IF(
          YEAR(B195)&gt;=2007,
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G195" s="6"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>45536</v>
       </c>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G196" s="6"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>45566</v>
       </c>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G197" s="6"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>45597</v>
       </c>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G198" s="6"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>45627</v>
       </c>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G199" s="6"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>45658</v>
       </c>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G200" s="6"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>45689</v>
       </c>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G201" s="6"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>45717</v>
       </c>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="G202" s="6"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>45748</v>
       </c>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G203" s="6"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>45778</v>
       </c>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G204" s="6"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>45809</v>
       </c>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="G205" s="6"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>45839</v>
       </c>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G206" s="6"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>45870</v>
       </c>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G207" s="6"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>45901</v>
       </c>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="G208" s="6"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>45931</v>
       </c>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="G209" s="6"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>45962</v>
       </c>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="G210" s="6"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>45992</v>
       </c>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G211" s="6"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>46023</v>
       </c>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="G212" s="6"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>46054</v>
       </c>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G213" s="6"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>46082</v>
       </c>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="G214" s="6"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>46113</v>
       </c>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="G215" s="6"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>46143</v>
       </c>
@@ -4635,6 +4635,24 @@
         <v>16100000.000000002</v>
       </c>
       <c r="G216" s="6"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B217" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C217" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D217" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E217" s="8">
+        <v>16500000</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E216">
@@ -4646,18 +4664,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88B153C-D992-477E-B6AF-040E6CE51A4F}">
-  <dimension ref="A1:F606"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F607"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -4677,7 +4695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>27760</v>
       </c>
@@ -4710,7 +4728,7 @@
         <v>885.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>27791</v>
       </c>
@@ -4743,7 +4761,7 @@
         <v>994.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>27820</v>
       </c>
@@ -4761,7 +4779,7 @@
         <v>1243.5999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>27851</v>
       </c>
@@ -4779,7 +4797,7 @@
         <v>1191.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>27881</v>
       </c>
@@ -4797,7 +4815,7 @@
         <v>1203.2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>27912</v>
       </c>
@@ -4815,7 +4833,7 @@
         <v>1254.7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>27942</v>
       </c>
@@ -4833,7 +4851,7 @@
         <v>1162.3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>27973</v>
       </c>
@@ -4851,7 +4869,7 @@
         <v>1026.0999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>28004</v>
       </c>
@@ -4869,7 +4887,7 @@
         <v>1057.9000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>28034</v>
       </c>
@@ -4887,7 +4905,7 @@
         <v>1129.4000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>28065</v>
       </c>
@@ -4905,7 +4923,7 @@
         <v>1084.4000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>28095</v>
       </c>
@@ -4923,7 +4941,7 @@
         <v>1061.8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>28126</v>
       </c>
@@ -4941,7 +4959,7 @@
         <v>969.9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>28157</v>
       </c>
@@ -4959,7 +4977,7 @@
         <v>1092.0999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>28185</v>
       </c>
@@ -4977,7 +4995,7 @@
         <v>1451.1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>28216</v>
       </c>
@@ -4995,7 +5013,7 @@
         <v>1354.4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>28246</v>
       </c>
@@ -5013,7 +5031,7 @@
         <v>1377.1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>28277</v>
       </c>
@@ -5031,7 +5049,7 @@
         <v>1459.8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>28307</v>
       </c>
@@ -5049,7 +5067,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>28338</v>
       </c>
@@ -5067,7 +5085,7 @@
         <v>1234.5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>28369</v>
       </c>
@@ -5085,7 +5103,7 @@
         <v>1104.5999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>28399</v>
       </c>
@@ -5103,7 +5121,7 @@
         <v>1341.3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>28430</v>
       </c>
@@ -5121,7 +5139,7 @@
         <v>1181.5999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>28460</v>
       </c>
@@ -5139,7 +5157,7 @@
         <v>1090.5999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>28491</v>
       </c>
@@ -5157,7 +5175,7 @@
         <v>931.3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>28522</v>
       </c>
@@ -5175,7 +5193,7 @@
         <v>1071.4000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>28550</v>
       </c>
@@ -5193,7 +5211,7 @@
         <v>1480.6</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28581</v>
       </c>
@@ -5211,7 +5229,7 @@
         <v>1406.5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>28611</v>
       </c>
@@ -5229,7 +5247,7 @@
         <v>1557.6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>28642</v>
       </c>
@@ -5247,7 +5265,7 @@
         <v>1549.4</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>28672</v>
       </c>
@@ -5265,7 +5283,7 @@
         <v>1289.2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>28703</v>
       </c>
@@ -5283,7 +5301,7 @@
         <v>1317.1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>28734</v>
       </c>
@@ -5301,7 +5319,7 @@
         <v>1103.5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>28764</v>
       </c>
@@ -5319,7 +5337,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>28795</v>
       </c>
@@ -5337,7 +5355,7 @@
         <v>1248.7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>28825</v>
       </c>
@@ -5355,7 +5373,7 @@
         <v>1068.5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>28856</v>
       </c>
@@ -5373,7 +5391,7 @@
         <v>1077.5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>28887</v>
       </c>
@@ -5391,7 +5409,7 @@
         <v>1148.7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>28915</v>
       </c>
@@ -5409,7 +5427,7 @@
         <v>1483.8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>28946</v>
       </c>
@@ -5427,7 +5445,7 @@
         <v>1304.5999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>28976</v>
       </c>
@@ -5445,7 +5463,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>29007</v>
       </c>
@@ -5463,7 +5481,7 @@
         <v>1183.8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>29037</v>
       </c>
@@ -5481,7 +5499,7 @@
         <v>1164.4000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>29068</v>
       </c>
@@ -5499,7 +5517,7 @@
         <v>1207.2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>29099</v>
       </c>
@@ -5517,7 +5535,7 @@
         <v>1029.5999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>29129</v>
       </c>
@@ -5535,7 +5553,7 @@
         <v>1197.5999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>29160</v>
       </c>
@@ -5553,7 +5571,7 @@
         <v>1018.6</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>29190</v>
       </c>
@@ -5571,7 +5589,7 @@
         <v>959.7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>29221</v>
       </c>
@@ -5589,7 +5607,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>29252</v>
       </c>
@@ -5607,7 +5625,7 @@
         <v>1038.7</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>29281</v>
       </c>
@@ -5625,7 +5643,7 @@
         <v>1141.9000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>29312</v>
       </c>
@@ -5643,7 +5661,7 @@
         <v>946.6</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>29342</v>
       </c>
@@ -5661,7 +5679,7 @@
         <v>893.8</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>29373</v>
       </c>
@@ -5679,7 +5697,7 @@
         <v>932.7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>29403</v>
       </c>
@@ -5697,7 +5715,7 @@
         <v>1006.6</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>29434</v>
       </c>
@@ -5715,7 +5733,7 @@
         <v>884.2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>29465</v>
       </c>
@@ -5733,7 +5751,7 @@
         <v>847.4</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>29495</v>
       </c>
@@ -5751,7 +5769,7 @@
         <v>1043.4000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>29526</v>
       </c>
@@ -5769,7 +5787,7 @@
         <v>870.5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>29556</v>
       </c>
@@ -5787,7 +5805,7 @@
         <v>821.4</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>29587</v>
       </c>
@@ -5805,7 +5823,7 @@
         <v>814.3</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>29618</v>
       </c>
@@ -5823,7 +5841,7 @@
         <v>949.2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>29646</v>
       </c>
@@ -5841,7 +5859,7 @@
         <v>1178.8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>29677</v>
       </c>
@@ -5859,7 +5877,7 @@
         <v>962.9</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>29707</v>
       </c>
@@ -5877,7 +5895,7 @@
         <v>933.1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>29738</v>
       </c>
@@ -5910,7 +5928,7 @@
         <v>942.7</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>29768</v>
       </c>
@@ -5928,7 +5946,7 @@
         <v>896.9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>29799</v>
       </c>
@@ -5946,7 +5964,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>29830</v>
       </c>
@@ -5964,7 +5982,7 @@
         <v>864.8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>29860</v>
       </c>
@@ -5982,7 +6000,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>29891</v>
       </c>
@@ -6000,7 +6018,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>29921</v>
       </c>
@@ -6018,7 +6036,7 @@
         <v>673.2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>29952</v>
       </c>
@@ -6036,7 +6054,7 @@
         <v>714.4</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>29983</v>
       </c>
@@ -6054,7 +6072,7 @@
         <v>840.5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>30011</v>
       </c>
@@ -6072,7 +6090,7 @@
         <v>1057.3</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>30042</v>
       </c>
@@ -6090,7 +6108,7 @@
         <v>877.2</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>30072</v>
       </c>
@@ -6108,7 +6126,7 @@
         <v>1020.2</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>30103</v>
       </c>
@@ -6126,7 +6144,7 @@
         <v>868.4</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>30133</v>
       </c>
@@ -6144,7 +6162,7 @@
         <v>827.4</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>30164</v>
       </c>
@@ -6162,7 +6180,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>30195</v>
       </c>
@@ -6180,7 +6198,7 @@
         <v>891.1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>30225</v>
       </c>
@@ -6198,7 +6216,7 @@
         <v>840.9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>30256</v>
       </c>
@@ -6216,7 +6234,7 @@
         <v>971.5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>30286</v>
       </c>
@@ -6234,7 +6252,7 @@
         <v>839.3</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>30317</v>
       </c>
@@ -6252,7 +6270,7 @@
         <v>789.3</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>30348</v>
       </c>
@@ -6270,7 +6288,7 @@
         <v>821.6</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>30376</v>
       </c>
@@ -6288,7 +6306,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>30407</v>
       </c>
@@ -6306,7 +6324,7 @@
         <v>1012.3</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>30437</v>
       </c>
@@ -6324,7 +6342,7 @@
         <v>1109.9000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>30468</v>
       </c>
@@ -6342,7 +6360,7 @@
         <v>1205.4000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>30498</v>
       </c>
@@ -6360,7 +6378,7 @@
         <v>1051.7</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>30529</v>
       </c>
@@ -6378,7 +6396,7 @@
         <v>993.1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>30560</v>
       </c>
@@ -6396,7 +6414,7 @@
         <v>980.4</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>30590</v>
       </c>
@@ -6414,7 +6432,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>30621</v>
       </c>
@@ -6432,7 +6450,7 @@
         <v>1050.2</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>30651</v>
       </c>
@@ -6450,7 +6468,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>30682</v>
       </c>
@@ -6468,7 +6486,7 @@
         <v>1056.9000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>30713</v>
       </c>
@@ -6486,7 +6504,7 @@
         <v>1158.9000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>30742</v>
       </c>
@@ -6504,7 +6522,7 @@
         <v>1351.5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>30773</v>
       </c>
@@ -6522,7 +6540,7 @@
         <v>1245.8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>30803</v>
       </c>
@@ -6540,7 +6558,7 @@
         <v>1451.7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>30834</v>
       </c>
@@ -6558,7 +6576,7 @@
         <v>1315.9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>30864</v>
       </c>
@@ -6576,7 +6594,7 @@
         <v>1237.2</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>30895</v>
       </c>
@@ -6594,7 +6612,7 @@
         <v>1129.5999999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>30926</v>
       </c>
@@ -6612,7 +6630,7 @@
         <v>1053.4000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>30956</v>
       </c>
@@ -6630,7 +6648,7 @@
         <v>1266.5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>30987</v>
       </c>
@@ -6648,7 +6666,7 @@
         <v>1141.0999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>31017</v>
       </c>
@@ -6666,7 +6684,7 @@
         <v>1074.8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>31048</v>
       </c>
@@ -6684,7 +6702,7 @@
         <v>1196.5999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>31079</v>
       </c>
@@ -6702,7 +6720,7 @@
         <v>1210.5999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>31107</v>
       </c>
@@ -6720,7 +6738,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>31138</v>
       </c>
@@ -6738,7 +6756,7 @@
         <v>1380.3</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>31168</v>
       </c>
@@ -6756,7 +6774,7 @@
         <v>1498.9</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>31199</v>
       </c>
@@ -6774,7 +6792,7 @@
         <v>1332.9</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>31229</v>
       </c>
@@ -6792,7 +6810,7 @@
         <v>1337.6</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>31260</v>
       </c>
@@ -6810,7 +6828,7 @@
         <v>1345.8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>31291</v>
       </c>
@@ -6828,7 +6846,7 @@
         <v>1463.5</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>31321</v>
       </c>
@@ -6846,7 +6864,7 @@
         <v>1243.2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>31352</v>
       </c>
@@ -6864,7 +6882,7 @@
         <v>1120.9000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>31382</v>
       </c>
@@ -6882,7 +6900,7 @@
         <v>1198.8</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>31413</v>
       </c>
@@ -6900,7 +6918,7 @@
         <v>1213.8</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>31444</v>
       </c>
@@ -6918,7 +6936,7 @@
         <v>1182.2</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>31472</v>
       </c>
@@ -6936,7 +6954,7 @@
         <v>1297.5999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>31503</v>
       </c>
@@ -6954,7 +6972,7 @@
         <v>1390.1</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>31533</v>
       </c>
@@ -6972,7 +6990,7 @@
         <v>1530.3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>31564</v>
       </c>
@@ -6990,7 +7008,7 @@
         <v>1426.5</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>31594</v>
       </c>
@@ -7008,7 +7026,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>31625</v>
       </c>
@@ -7026,7 +7044,7 @@
         <v>1344.1</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>31656</v>
       </c>
@@ -7044,7 +7062,7 @@
         <v>1733.6</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>31686</v>
       </c>
@@ -7077,7 +7095,7 @@
         <v>1270.5999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>31717</v>
       </c>
@@ -7095,7 +7113,7 @@
         <v>1119.9000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>31747</v>
       </c>
@@ -7113,7 +7131,7 @@
         <v>1431.1</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>31778</v>
       </c>
@@ -7131,7 +7149,7 @@
         <v>918.9</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>31809</v>
       </c>
@@ -7149,7 +7167,7 @@
         <v>1148.4000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>31837</v>
       </c>
@@ -7167,7 +7185,7 @@
         <v>1381.7</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>31868</v>
       </c>
@@ -7185,7 +7203,7 @@
         <v>1385.3</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>31898</v>
       </c>
@@ -7203,7 +7221,7 @@
         <v>1298.5</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>31929</v>
       </c>
@@ -7221,7 +7239,7 @@
         <v>1419.6</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>31959</v>
       </c>
@@ -7239,7 +7257,7 @@
         <v>1355.8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>31990</v>
       </c>
@@ -7257,7 +7275,7 @@
         <v>1400.6</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>32021</v>
       </c>
@@ -7275,7 +7293,7 @@
         <v>1300.5</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>32051</v>
       </c>
@@ -7293,7 +7311,7 @@
         <v>1193.2</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>32082</v>
       </c>
@@ -7311,7 +7329,7 @@
         <v>1110.7</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>32112</v>
       </c>
@@ -7329,7 +7347,7 @@
         <v>1249.2</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>32143</v>
       </c>
@@ -7347,7 +7365,7 @@
         <v>1122.5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>32174</v>
       </c>
@@ -7365,7 +7383,7 @@
         <v>1308.8</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>32203</v>
       </c>
@@ -7383,7 +7401,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>32234</v>
       </c>
@@ -7401,7 +7419,7 @@
         <v>1333.5</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>32264</v>
       </c>
@@ -7419,7 +7437,7 @@
         <v>1455.4</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>32295</v>
       </c>
@@ -7437,7 +7455,7 @@
         <v>1483.1</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>32325</v>
       </c>
@@ -7455,7 +7473,7 @@
         <v>1302.8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>32356</v>
       </c>
@@ -7473,7 +7491,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>32387</v>
       </c>
@@ -7491,7 +7509,7 @@
         <v>1223.2</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>32417</v>
       </c>
@@ -7509,7 +7527,7 @@
         <v>1249.9000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>32448</v>
       </c>
@@ -7527,7 +7545,7 @@
         <v>1191.0999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>32478</v>
       </c>
@@ -7545,7 +7563,7 @@
         <v>1285.2</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>32509</v>
       </c>
@@ -7563,7 +7581,7 @@
         <v>1084.2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>32540</v>
       </c>
@@ -7581,7 +7599,7 @@
         <v>1127.3</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>32568</v>
       </c>
@@ -7599,7 +7617,7 @@
         <v>1337.6</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>32599</v>
       </c>
@@ -7617,7 +7635,7 @@
         <v>1354.8</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>32629</v>
       </c>
@@ -7635,7 +7653,7 @@
         <v>1438.4</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>32660</v>
       </c>
@@ -7653,7 +7671,7 @@
         <v>1329.2</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>32690</v>
       </c>
@@ -7671,7 +7689,7 @@
         <v>1279.0999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>32721</v>
       </c>
@@ -7689,7 +7707,7 @@
         <v>1441.9</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>32752</v>
       </c>
@@ -7707,7 +7725,7 @@
         <v>1263.8</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>32782</v>
       </c>
@@ -7725,7 +7743,7 @@
         <v>1116.9000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>32813</v>
       </c>
@@ -7743,7 +7761,7 @@
         <v>1047.5999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>32843</v>
       </c>
@@ -7761,7 +7779,7 @@
         <v>1011.9</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>32874</v>
       </c>
@@ -7779,7 +7797,7 @@
         <v>1161.3</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>32905</v>
       </c>
@@ -7797,7 +7815,7 @@
         <v>1073.4000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>32933</v>
       </c>
@@ -7815,7 +7833,7 @@
         <v>1295.2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>32964</v>
       </c>
@@ -7833,7 +7851,7 @@
         <v>1226.3</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>32994</v>
       </c>
@@ -7851,7 +7869,7 @@
         <v>1332.1</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>33025</v>
       </c>
@@ -7869,7 +7887,7 @@
         <v>1306.0999999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>33055</v>
       </c>
@@ -7887,7 +7905,7 @@
         <v>1244.4000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>33086</v>
       </c>
@@ -7905,7 +7923,7 @@
         <v>1196.9000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>33117</v>
       </c>
@@ -7923,7 +7941,7 @@
         <v>1144.8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>33147</v>
       </c>
@@ -7941,7 +7959,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>33178</v>
       </c>
@@ -7959,7 +7977,7 @@
         <v>1000.5</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>33208</v>
       </c>
@@ -7977,7 +7995,7 @@
         <v>987.2</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>33239</v>
       </c>
@@ -7995,7 +8013,7 @@
         <v>839.3</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>33270</v>
       </c>
@@ -8013,7 +8031,7 @@
         <v>927.5</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>33298</v>
       </c>
@@ -8031,7 +8049,7 @@
         <v>1103.0999999999999</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>33329</v>
       </c>
@@ -8049,7 +8067,7 @@
         <v>1059.5999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>33359</v>
       </c>
@@ -8067,7 +8085,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>33390</v>
       </c>
@@ -8085,7 +8103,7 @@
         <v>1175.3</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>33420</v>
       </c>
@@ -8103,7 +8121,7 @@
         <v>1185.2</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>33451</v>
       </c>
@@ -8121,7 +8139,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>33482</v>
       </c>
@@ -8139,7 +8157,7 @@
         <v>1062.2</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>33512</v>
       </c>
@@ -8157,7 +8175,7 @@
         <v>1047.5999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>33543</v>
       </c>
@@ -8175,7 +8193,7 @@
         <v>932.1</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>33573</v>
       </c>
@@ -8193,7 +8211,7 @@
         <v>961.5</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>33604</v>
       </c>
@@ -8211,7 +8229,7 @@
         <v>867.8</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>33635</v>
       </c>
@@ -8244,7 +8262,7 @@
         <v>988.5</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>33664</v>
       </c>
@@ -8262,7 +8280,7 @@
         <v>1128.4000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>33695</v>
       </c>
@@ -8280,7 +8298,7 @@
         <v>1144.9000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>33725</v>
       </c>
@@ -8298,7 +8316,7 @@
         <v>1169.7</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>33756</v>
       </c>
@@ -8316,7 +8334,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>33786</v>
       </c>
@@ -8334,7 +8352,7 @@
         <v>1158.2</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>33817</v>
       </c>
@@ -8352,7 +8370,7 @@
         <v>1065.2</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>33848</v>
       </c>
@@ -8370,7 +8388,7 @@
         <v>1095.4000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>33878</v>
       </c>
@@ -8388,7 +8406,7 @@
         <v>1132.2</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>33909</v>
       </c>
@@ -8406,7 +8424,7 @@
         <v>988.6</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>33939</v>
       </c>
@@ -8424,7 +8442,7 @@
         <v>1070.7</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>33970</v>
       </c>
@@ -8442,7 +8460,7 @@
         <v>915.3</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>34001</v>
       </c>
@@ -8460,7 +8478,7 @@
         <v>976.1</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>34029</v>
       </c>
@@ -8478,7 +8496,7 @@
         <v>1228.9000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>34060</v>
       </c>
@@ -8496,7 +8514,7 @@
         <v>1273.5</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>34090</v>
       </c>
@@ -8514,7 +8532,7 @@
         <v>1342.2</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>34121</v>
       </c>
@@ -8532,7 +8550,7 @@
         <v>1383.1</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>34151</v>
       </c>
@@ -8550,7 +8568,7 @@
         <v>1266.9000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>34182</v>
       </c>
@@ -8568,7 +8586,7 @@
         <v>1158.8</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>34213</v>
       </c>
@@ -8586,7 +8604,7 @@
         <v>1164.5999999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>34243</v>
       </c>
@@ -8604,7 +8622,7 @@
         <v>1182.5</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>34274</v>
       </c>
@@ -8622,7 +8640,7 @@
         <v>1140.9000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>34304</v>
       </c>
@@ -8640,7 +8658,7 @@
         <v>1152.7</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>34335</v>
       </c>
@@ -8658,7 +8676,7 @@
         <v>1045.5</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>34366</v>
       </c>
@@ -8676,7 +8694,7 @@
         <v>1170.9000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>34394</v>
       </c>
@@ -8694,7 +8712,7 @@
         <v>1472.2</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>34425</v>
       </c>
@@ -8712,7 +8730,7 @@
         <v>1337.9</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>34455</v>
       </c>
@@ -8730,7 +8748,7 @@
         <v>1382.1</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>34486</v>
       </c>
@@ -8748,7 +8766,7 @@
         <v>1479.6</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>34516</v>
       </c>
@@ -8766,7 +8784,7 @@
         <v>1219.5</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>34547</v>
       </c>
@@ -8784,7 +8802,7 @@
         <v>1329.3</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>34578</v>
       </c>
@@ -8802,7 +8820,7 @@
         <v>1252.0999999999999</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>34608</v>
       </c>
@@ -8820,7 +8838,7 @@
         <v>1291.8</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>34639</v>
       </c>
@@ -8838,7 +8856,7 @@
         <v>1197.9000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>34669</v>
       </c>
@@ -8856,7 +8874,7 @@
         <v>1218.9000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>34700</v>
       </c>
@@ -8874,7 +8892,7 @@
         <v>1031.5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>34731</v>
       </c>
@@ -8892,7 +8910,7 @@
         <v>1128.7</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>34759</v>
       </c>
@@ -8910,7 +8928,7 @@
         <v>1403.3</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>34790</v>
       </c>
@@ -8928,7 +8946,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>34820</v>
       </c>
@@ -8946,7 +8964,7 @@
         <v>1427.5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>34851</v>
       </c>
@@ -8964,7 +8982,7 @@
         <v>1477.2</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>34881</v>
       </c>
@@ -8982,7 +9000,7 @@
         <v>1255.3</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>34912</v>
       </c>
@@ -9000,7 +9018,7 @@
         <v>1365.2</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>34943</v>
       </c>
@@ -9018,7 +9036,7 @@
         <v>1214.4000000000001</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>34973</v>
       </c>
@@ -9036,7 +9054,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>35004</v>
       </c>
@@ -9054,7 +9072,7 @@
         <v>1169.0999999999999</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>35034</v>
       </c>
@@ -9072,7 +9090,7 @@
         <v>1202.5999999999999</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>35065</v>
       </c>
@@ -9090,7 +9108,7 @@
         <v>1050.5999999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>35096</v>
       </c>
@@ -9108,7 +9126,7 @@
         <v>1237.9000000000001</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>35125</v>
       </c>
@@ -9126,7 +9144,7 @@
         <v>1404.4</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>35156</v>
       </c>
@@ -9144,7 +9162,7 @@
         <v>1359.3</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>35186</v>
       </c>
@@ -9162,7 +9180,7 @@
         <v>1522.9</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>35217</v>
       </c>
@@ -9180,7 +9198,7 @@
         <v>1404.2</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>35247</v>
       </c>
@@ -9198,7 +9216,7 @@
         <v>1317.3</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>35278</v>
       </c>
@@ -9216,7 +9234,7 @@
         <v>1333.4</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>35309</v>
       </c>
@@ -9234,7 +9252,7 @@
         <v>1231.4000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>35339</v>
       </c>
@@ -9252,7 +9270,7 @@
         <v>1296.5999999999999</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>35370</v>
       </c>
@@ -9270,7 +9288,7 @@
         <v>1146.4000000000001</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>35400</v>
       </c>
@@ -9288,7 +9306,7 @@
         <v>1151.8</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>35431</v>
       </c>
@@ -9306,7 +9324,7 @@
         <v>1114.5999999999999</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>35462</v>
       </c>
@@ -9324,7 +9342,7 @@
         <v>1177.4000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>35490</v>
       </c>
@@ -9342,7 +9360,7 @@
         <v>1425.9</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>35521</v>
       </c>
@@ -9360,7 +9378,7 @@
         <v>1310.3</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>35551</v>
       </c>
@@ -9378,7 +9396,7 @@
         <v>1435.8</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>35582</v>
       </c>
@@ -9411,7 +9429,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>35612</v>
       </c>
@@ -9429,7 +9447,7 @@
         <v>1376.6</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>35643</v>
       </c>
@@ -9447,7 +9465,7 @@
         <v>1348.2</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>35674</v>
       </c>
@@ -9465,7 +9483,7 @@
         <v>1238.5</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>35704</v>
       </c>
@@ -9483,7 +9501,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>35735</v>
       </c>
@@ -9501,7 +9519,7 @@
         <v>1146.0999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>35765</v>
       </c>
@@ -9519,7 +9537,7 @@
         <v>1287.7</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>35796</v>
       </c>
@@ -9537,7 +9555,7 @@
         <v>1044.0999999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>35827</v>
       </c>
@@ -9555,7 +9573,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>35855</v>
       </c>
@@ -9573,7 +9591,7 @@
         <v>1405.5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>35886</v>
       </c>
@@ -9591,7 +9609,7 @@
         <v>1390.9</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>35916</v>
       </c>
@@ -9609,7 +9627,7 @@
         <v>1543.9</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>35947</v>
       </c>
@@ -9627,7 +9645,7 @@
         <v>1606.6</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>35977</v>
       </c>
@@ -9645,7 +9663,7 @@
         <v>1264.9000000000001</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>36008</v>
       </c>
@@ -9663,7 +9681,7 @@
         <v>1265.0999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>36039</v>
       </c>
@@ -9681,7 +9699,7 @@
         <v>1314.4</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>36069</v>
       </c>
@@ -9699,7 +9717,7 @@
         <v>1407.5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>36100</v>
       </c>
@@ -9717,7 +9735,7 @@
         <v>1176.4000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>36130</v>
       </c>
@@ -9735,7 +9753,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>36161</v>
       </c>
@@ -9753,7 +9771,7 @@
         <v>1123.7</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>36192</v>
       </c>
@@ -9771,7 +9789,7 @@
         <v>1325.7</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>36220</v>
       </c>
@@ -9789,7 +9807,7 @@
         <v>1580.2</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>36251</v>
       </c>
@@ -9807,7 +9825,7 @@
         <v>1451.7</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>36281</v>
       </c>
@@ -9825,7 +9843,7 @@
         <v>1632.6</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>36312</v>
       </c>
@@ -9843,7 +9861,7 @@
         <v>1651.4</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>36342</v>
       </c>
@@ -9861,7 +9879,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>36373</v>
       </c>
@@ -9879,7 +9897,7 @@
         <v>1523.6</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>36404</v>
       </c>
@@ -9897,7 +9915,7 @@
         <v>1442.5</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>36434</v>
       </c>
@@ -9915,7 +9933,7 @@
         <v>1396.8</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>36465</v>
       </c>
@@ -9933,7 +9951,7 @@
         <v>1317.2</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>36495</v>
       </c>
@@ -9951,7 +9969,7 @@
         <v>1440.6</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>36526</v>
       </c>
@@ -9969,7 +9987,7 @@
         <v>1239.3</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>36557</v>
       </c>
@@ -9987,7 +10005,7 @@
         <v>1539.3</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>36586</v>
       </c>
@@ -10005,7 +10023,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>36617</v>
       </c>
@@ -10023,7 +10041,7 @@
         <v>1538.9</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>36647</v>
       </c>
@@ -10041,7 +10059,7 @@
         <v>1664.9</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>36678</v>
       </c>
@@ -10059,7 +10077,7 @@
         <v>1662.7</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>36708</v>
       </c>
@@ -10077,7 +10095,7 @@
         <v>1468.6</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>36739</v>
       </c>
@@ -10095,7 +10113,7 @@
         <v>1578.8</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>36770</v>
       </c>
@@ -10113,7 +10131,7 @@
         <v>1506.3</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>36800</v>
       </c>
@@ -10131,7 +10149,7 @@
         <v>1367.7</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>36831</v>
       </c>
@@ -10149,7 +10167,7 @@
         <v>1260.9000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>36861</v>
       </c>
@@ -10167,7 +10185,7 @@
         <v>1271.2</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>36892</v>
       </c>
@@ -10185,7 +10203,7 @@
         <v>1196.3</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>36923</v>
       </c>
@@ -10203,7 +10221,7 @@
         <v>1381.5</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>36951</v>
       </c>
@@ -10221,7 +10239,7 @@
         <v>1627.8</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>36982</v>
       </c>
@@ -10239,7 +10257,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>37012</v>
       </c>
@@ -10257,7 +10275,7 @@
         <v>1635.2</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>37043</v>
       </c>
@@ -10275,7 +10293,7 @@
         <v>1652.2</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>37073</v>
       </c>
@@ -10293,7 +10311,7 @@
         <v>1374.6</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>37104</v>
       </c>
@@ -10311,7 +10329,7 @@
         <v>1478.2</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>37135</v>
       </c>
@@ -10329,7 +10347,7 @@
         <v>1312.5</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>37165</v>
       </c>
@@ -10347,7 +10365,7 @@
         <v>1753.2</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>37196</v>
       </c>
@@ -10365,7 +10383,7 @@
         <v>1347.9</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>37226</v>
       </c>
@@ -10383,7 +10401,7 @@
         <v>1336.1</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>37257</v>
       </c>
@@ -10401,7 +10419,7 @@
         <v>1129.999</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>37288</v>
       </c>
@@ -10419,7 +10437,7 @@
         <v>1328.7550000000001</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>37316</v>
       </c>
@@ -10437,7 +10455,7 @@
         <v>1541.2149999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>37347</v>
       </c>
@@ -10455,7 +10473,7 @@
         <v>1471.8009999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>37377</v>
       </c>
@@ -10473,7 +10491,7 @@
         <v>1538.4960000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>37408</v>
       </c>
@@ -10491,7 +10509,7 @@
         <v>1563.9380000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>37438</v>
       </c>
@@ -10509,7 +10527,7 @@
         <v>1551.9960000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>37469</v>
       </c>
@@ -10527,7 +10545,7 @@
         <v>1734.9559999999999</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>37500</v>
       </c>
@@ -10545,7 +10563,7 @@
         <v>1250.9860000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>37530</v>
       </c>
@@ -10578,7 +10596,7 @@
         <v>1331.09</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>37561</v>
       </c>
@@ -10596,7 +10614,7 @@
         <v>1227.557</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>37591</v>
       </c>
@@ -10614,7 +10632,7 @@
         <v>1467.7080000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>37622</v>
       </c>
@@ -10632,7 +10650,7 @@
         <v>1108.279</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>37653</v>
       </c>
@@ -10650,7 +10668,7 @@
         <v>1237.6189999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>37681</v>
       </c>
@@ -10668,7 +10686,7 @@
         <v>1474.819</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>37712</v>
       </c>
@@ -10686,7 +10704,7 @@
         <v>1436.7329999999999</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>37742</v>
       </c>
@@ -10704,7 +10722,7 @@
         <v>1601.145</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>37773</v>
       </c>
@@ -10722,7 +10740,7 @@
         <v>1502.328</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>37803</v>
       </c>
@@ -10740,7 +10758,7 @@
         <v>1538.7809999999999</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>37834</v>
       </c>
@@ -10758,7 +10776,7 @@
         <v>1656.1669999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>37865</v>
       </c>
@@ -10776,7 +10794,7 @@
         <v>1329.499</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>37895</v>
       </c>
@@ -10794,7 +10812,7 @@
         <v>1333.4970000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>37926</v>
       </c>
@@ -10812,7 +10830,7 @@
         <v>1285.3599999999999</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>37956</v>
       </c>
@@ -10830,7 +10848,7 @@
         <v>1463.2639999999999</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>37987</v>
       </c>
@@ -10848,7 +10866,7 @@
         <v>1149.6679999999999</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
         <v>38018</v>
       </c>
@@ -10866,7 +10884,7 @@
         <v>1303.7180000000001</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>38047</v>
       </c>
@@ -10884,7 +10902,7 @@
         <v>1540.3209999999999</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
         <v>38078</v>
       </c>
@@ -10902,7 +10920,7 @@
         <v>1455.643</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>38108</v>
       </c>
@@ -10920,7 +10938,7 @@
         <v>1660.854</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" s="2">
         <v>38139</v>
       </c>
@@ -10938,7 +10956,7 @@
         <v>1480.758</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" s="2">
         <v>38169</v>
       </c>
@@ -10956,7 +10974,7 @@
         <v>1589.173</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" s="2">
         <v>38200</v>
       </c>
@@ -10974,7 +10992,7 @@
         <v>1463.4090000000001</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" s="2">
         <v>38231</v>
       </c>
@@ -10992,7 +11010,7 @@
         <v>1470.0809999999999</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" s="2">
         <v>38261</v>
       </c>
@@ -11010,7 +11028,7 @@
         <v>1370.0930000000001</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" s="2">
         <v>38292</v>
       </c>
@@ -11028,7 +11046,7 @@
         <v>1231.1969999999999</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" s="2">
         <v>38322</v>
       </c>
@@ -11046,7 +11064,7 @@
         <v>1583.6030000000001</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" s="2">
         <v>38353</v>
       </c>
@@ -11064,7 +11082,7 @@
         <v>1095.8510000000001</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" s="2">
         <v>38384</v>
       </c>
@@ -11082,7 +11100,7 @@
         <v>1286.0740000000001</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" s="2">
         <v>38412</v>
       </c>
@@ -11100,7 +11118,7 @@
         <v>1615.9829999999999</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" s="2">
         <v>38443</v>
       </c>
@@ -11118,7 +11136,7 @@
         <v>1542.0509999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" s="2">
         <v>38473</v>
       </c>
@@ -11136,7 +11154,7 @@
         <v>1537.3209999999999</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" s="2">
         <v>38504</v>
       </c>
@@ -11154,7 +11172,7 @@
         <v>1720.0060000000001</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" s="2">
         <v>38534</v>
       </c>
@@ -11172,7 +11190,7 @@
         <v>1845.713</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" s="2">
         <v>38565</v>
       </c>
@@ -11190,7 +11208,7 @@
         <v>1524.1579999999999</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" s="2">
         <v>38596</v>
       </c>
@@ -11208,7 +11226,7 @@
         <v>1366.93</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" s="2">
         <v>38626</v>
       </c>
@@ -11226,7 +11244,7 @@
         <v>1184.1600000000001</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" s="2">
         <v>38657</v>
       </c>
@@ -11244,7 +11262,7 @@
         <v>1200.7860000000001</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" s="2">
         <v>38687</v>
       </c>
@@ -11262,7 +11280,7 @@
         <v>1525.713</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" s="2">
         <v>38718</v>
       </c>
@@ -11280,7 +11298,7 @@
         <v>1176.162</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" s="2">
         <v>38749</v>
       </c>
@@ -11298,7 +11316,7 @@
         <v>1298.1300000000001</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" s="2">
         <v>38777</v>
       </c>
@@ -11316,7 +11334,7 @@
         <v>1576.6469999999999</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="2">
         <v>38808</v>
       </c>
@@ -11334,7 +11352,7 @@
         <v>1489.8040000000001</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" s="2">
         <v>38838</v>
       </c>
@@ -11352,7 +11370,7 @@
         <v>1533.712</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A367" s="2">
         <v>38869</v>
       </c>
@@ -11370,7 +11388,7 @@
         <v>1545.268</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" s="2">
         <v>38899</v>
       </c>
@@ -11388,7 +11406,7 @@
         <v>1531.114</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" s="2">
         <v>38930</v>
       </c>
@@ -11406,7 +11424,7 @@
         <v>1530.0139999999999</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" s="2">
         <v>38961</v>
       </c>
@@ -11424,7 +11442,7 @@
         <v>1394.2149999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" s="2">
         <v>38991</v>
       </c>
@@ -11442,7 +11460,7 @@
         <v>1260.626</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" s="2">
         <v>39022</v>
       </c>
@@ -11460,7 +11478,7 @@
         <v>1236.5840000000001</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" s="2">
         <v>39052</v>
       </c>
@@ -11478,7 +11496,7 @@
         <v>1476.413</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" s="2">
         <v>39083</v>
       </c>
@@ -11496,7 +11514,7 @@
         <v>1124.2159999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" s="2">
         <v>39114</v>
       </c>
@@ -11514,7 +11532,7 @@
         <v>1285.136</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" s="2">
         <v>39142</v>
       </c>
@@ -11532,7 +11550,7 @@
         <v>1574.877</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" s="2">
         <v>39173</v>
       </c>
@@ -11550,7 +11568,7 @@
         <v>1365.9649999999999</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" s="2">
         <v>39203</v>
       </c>
@@ -11568,7 +11586,7 @@
         <v>1590.2619999999999</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" s="2">
         <v>39234</v>
       </c>
@@ -11586,7 +11604,7 @@
         <v>1481.21</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" s="2">
         <v>39264</v>
       </c>
@@ -11604,7 +11622,7 @@
         <v>1331.0239999999999</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" s="2">
         <v>39295</v>
       </c>
@@ -11622,7 +11640,7 @@
         <v>1500.386</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" s="2">
         <v>39326</v>
       </c>
@@ -11640,7 +11658,7 @@
         <v>1335.8140000000001</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" s="2">
         <v>39356</v>
       </c>
@@ -11658,7 +11676,7 @@
         <v>1256.5329999999999</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" s="2">
         <v>39387</v>
       </c>
@@ -11676,7 +11694,7 @@
         <v>1200.511</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" s="2">
         <v>39417</v>
       </c>
@@ -11694,7 +11712,7 @@
         <v>1414.1469999999999</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" s="2">
         <v>39448</v>
       </c>
@@ -11712,7 +11730,7 @@
         <v>1063.4079999999999</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" s="2">
         <v>39479</v>
       </c>
@@ -11745,7 +11763,7 @@
         <v>1196.431</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" s="2">
         <v>39508</v>
       </c>
@@ -11763,7 +11781,7 @@
         <v>1378.605</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" s="2">
         <v>39539</v>
       </c>
@@ -11781,7 +11799,7 @@
         <v>1272.999</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" s="2">
         <v>39569</v>
       </c>
@@ -11799,7 +11817,7 @@
         <v>1420.4849999999999</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" s="2">
         <v>39600</v>
       </c>
@@ -11817,7 +11835,7 @@
         <v>1212.54</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" s="2">
         <v>39630</v>
       </c>
@@ -11835,7 +11853,7 @@
         <v>1156.0029999999999</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393" s="2">
         <v>39661</v>
       </c>
@@ -11853,7 +11871,7 @@
         <v>1269.1130000000001</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" s="2">
         <v>39692</v>
       </c>
@@ -11871,7 +11889,7 @@
         <v>984.59199999999998</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" s="2">
         <v>39722</v>
       </c>
@@ -11889,7 +11907,7 @@
         <v>859.02599999999995</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" s="2">
         <v>39753</v>
       </c>
@@ -11907,7 +11925,7 @@
         <v>763.93600000000004</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" s="2">
         <v>39783</v>
       </c>
@@ -11925,7 +11943,7 @@
         <v>916.12</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" s="2">
         <v>39814</v>
       </c>
@@ -11943,7 +11961,7 @@
         <v>670.46600000000001</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" s="2">
         <v>39845</v>
       </c>
@@ -11961,7 +11979,7 @@
         <v>701.63499999999999</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" s="2">
         <v>39873</v>
       </c>
@@ -11979,7 +11997,7 @@
         <v>872.84799999999996</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" s="2">
         <v>39904</v>
       </c>
@@ -11997,7 +12015,7 @@
         <v>832.58799999999997</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" s="2">
         <v>39934</v>
       </c>
@@ -12015,7 +12033,7 @@
         <v>938.41</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" s="2">
         <v>39965</v>
       </c>
@@ -12033,7 +12051,7 @@
         <v>874.87400000000002</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" s="2">
         <v>39995</v>
       </c>
@@ -12051,7 +12069,7 @@
         <v>1011.769</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A405" s="2">
         <v>40026</v>
       </c>
@@ -12069,7 +12087,7 @@
         <v>1274.6780000000001</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" s="2">
         <v>40057</v>
       </c>
@@ -12087,7 +12105,7 @@
         <v>759.63300000000004</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" s="2">
         <v>40087</v>
       </c>
@@ -12105,7 +12123,7 @@
         <v>853.94200000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" s="2">
         <v>40118</v>
       </c>
@@ -12123,7 +12141,7 @@
         <v>761.86500000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" s="2">
         <v>40148</v>
       </c>
@@ -12141,7 +12159,7 @@
         <v>1049.27</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" s="2">
         <v>40179</v>
       </c>
@@ -12159,7 +12177,7 @@
         <v>712.46900000000005</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" s="2">
         <v>40210</v>
       </c>
@@ -12177,7 +12195,7 @@
         <v>793.36199999999997</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" s="2">
         <v>40238</v>
       </c>
@@ -12195,7 +12213,7 @@
         <v>1083.953</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" s="2">
         <v>40269</v>
       </c>
@@ -12213,7 +12231,7 @@
         <v>997.33399999999995</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A414" s="2">
         <v>40299</v>
       </c>
@@ -12231,7 +12249,7 @@
         <v>1117.57</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A415" s="2">
         <v>40330</v>
       </c>
@@ -12249,7 +12267,7 @@
         <v>1000.455</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A416" s="2">
         <v>40360</v>
       </c>
@@ -12267,7 +12285,7 @@
         <v>1065.748</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A417" s="2">
         <v>40391</v>
       </c>
@@ -12285,7 +12303,7 @@
         <v>1011.564</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A418" s="2">
         <v>40422</v>
       </c>
@@ -12303,7 +12321,7 @@
         <v>973.95399999999995</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A419" s="2">
         <v>40452</v>
       </c>
@@ -12321,7 +12339,7 @@
         <v>965.13499999999999</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A420" s="2">
         <v>40483</v>
       </c>
@@ -12339,7 +12357,7 @@
         <v>888.08500000000004</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A421" s="2">
         <v>40513</v>
       </c>
@@ -12357,7 +12375,7 @@
         <v>1162.8969999999999</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A422" s="2">
         <v>40544</v>
       </c>
@@ -12375,7 +12393,7 @@
         <v>836.36599999999999</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A423" s="2">
         <v>40575</v>
       </c>
@@ -12393,7 +12411,7 @@
         <v>1007.082</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A424" s="2">
         <v>40603</v>
       </c>
@@ -12411,7 +12429,7 @@
         <v>1276.8430000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A425" s="2">
         <v>40634</v>
       </c>
@@ -12429,7 +12447,7 @@
         <v>1173.52</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A426" s="2">
         <v>40664</v>
       </c>
@@ -12447,7 +12465,7 @@
         <v>1081.2719999999999</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A427" s="2">
         <v>40695</v>
       </c>
@@ -12465,7 +12483,7 @@
         <v>1071.229</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A428" s="2">
         <v>40725</v>
       </c>
@@ -12483,7 +12501,7 @@
         <v>1086.0640000000001</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A429" s="2">
         <v>40756</v>
       </c>
@@ -12501,7 +12519,7 @@
         <v>1094.479</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A430" s="2">
         <v>40787</v>
       </c>
@@ -12519,7 +12537,7 @@
         <v>1076.037</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A431" s="2">
         <v>40817</v>
       </c>
@@ -12537,7 +12555,7 @@
         <v>1048.258</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A432" s="2">
         <v>40848</v>
       </c>
@@ -12555,7 +12573,7 @@
         <v>1028.7739999999999</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" s="2">
         <v>40878</v>
       </c>
@@ -12573,7 +12591,7 @@
         <v>1268.462</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A434" s="2">
         <v>40909</v>
       </c>
@@ -12591,7 +12609,7 @@
         <v>938.17</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A435" s="2">
         <v>40940</v>
       </c>
@@ -12609,7 +12627,7 @@
         <v>1175.82</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" s="2">
         <v>40969</v>
       </c>
@@ -12627,7 +12645,7 @@
         <v>1434.0039999999999</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A437" s="2">
         <v>41000</v>
       </c>
@@ -12645,7 +12663,7 @@
         <v>1204.471</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" s="2">
         <v>41030</v>
       </c>
@@ -12663,7 +12681,7 @@
         <v>1369.4929999999999</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" s="2">
         <v>41061</v>
       </c>
@@ -12681,7 +12699,7 @@
         <v>1310.1579999999999</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" s="2">
         <v>41091</v>
       </c>
@@ -12699,7 +12717,7 @@
         <v>1171.809</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A441" s="2">
         <v>41122</v>
       </c>
@@ -12717,7 +12735,7 @@
         <v>1305.3420000000001</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A442" s="2">
         <v>41153</v>
       </c>
@@ -12735,7 +12753,7 @@
         <v>1206.182</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A443" s="2">
         <v>41183</v>
       </c>
@@ -12753,7 +12771,7 @@
         <v>1119.1479999999999</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A444" s="2">
         <v>41214</v>
       </c>
@@ -12771,7 +12789,7 @@
         <v>1169.8030000000001</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A445" s="2">
         <v>41244</v>
       </c>
@@ -12789,7 +12807,7 @@
         <v>1375.0840000000001</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A446" s="2">
         <v>41275</v>
       </c>
@@ -12807,7 +12825,7 @@
         <v>1065.798</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A447" s="2">
         <v>41306</v>
       </c>
@@ -12825,7 +12843,7 @@
         <v>1217.8579999999999</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A448" s="2">
         <v>41334</v>
       </c>
@@ -12843,7 +12861,7 @@
         <v>1479.4269999999999</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A449" s="2">
         <v>41365</v>
       </c>
@@ -12861,7 +12879,7 @@
         <v>1313.768</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A450" s="2">
         <v>41395</v>
       </c>
@@ -12879,7 +12897,7 @@
         <v>1473.2750000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A451" s="2">
         <v>41426</v>
       </c>
@@ -12912,7 +12930,7 @@
         <v>1425.8019999999999</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A452" s="2">
         <v>41456</v>
       </c>
@@ -12930,7 +12948,7 @@
         <v>1335.8330000000001</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A453" s="2">
         <v>41487</v>
       </c>
@@ -12948,7 +12966,7 @@
         <v>1527.4829999999999</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A454" s="2">
         <v>41518</v>
       </c>
@@ -12966,7 +12984,7 @@
         <v>1152.8140000000001</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A455" s="2">
         <v>41548</v>
       </c>
@@ -12984,7 +13002,7 @@
         <v>1235.5319999999999</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A456" s="2">
         <v>41579</v>
       </c>
@@ -13002,7 +13020,7 @@
         <v>1271.4459999999999</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A457" s="2">
         <v>41609</v>
       </c>
@@ -13020,7 +13038,7 @@
         <v>1383.6759999999999</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A458" s="2">
         <v>41640</v>
       </c>
@@ -13038,7 +13056,7 @@
         <v>1043.019</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A459" s="2">
         <v>41671</v>
       </c>
@@ -13056,7 +13074,7 @@
         <v>1221.3699999999999</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A460" s="2">
         <v>41699</v>
       </c>
@@ -13074,7 +13092,7 @@
         <v>1562.748</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A461" s="2">
         <v>41730</v>
       </c>
@@ -13092,7 +13110,7 @@
         <v>1408.232</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A462" s="2">
         <v>41760</v>
       </c>
@@ -13110,7 +13128,7 @@
         <v>1644.367</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A463" s="2">
         <v>41791</v>
       </c>
@@ -13128,7 +13146,7 @@
         <v>1451.8140000000001</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A464" s="2">
         <v>41821</v>
       </c>
@@ -13146,7 +13164,7 @@
         <v>1473.962</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465" s="2">
         <v>41852</v>
       </c>
@@ -13164,7 +13182,7 @@
         <v>1607.3150000000001</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466" s="2">
         <v>41883</v>
       </c>
@@ -13182,7 +13200,7 @@
         <v>1272.0360000000001</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467" s="2">
         <v>41913</v>
       </c>
@@ -13200,7 +13218,7 @@
         <v>1312.329</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A468" s="2">
         <v>41944</v>
       </c>
@@ -13218,7 +13236,7 @@
         <v>1324.117</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A469" s="2">
         <v>41974</v>
       </c>
@@ -13236,7 +13254,7 @@
         <v>1538.5340000000001</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470" s="2">
         <v>42005</v>
       </c>
@@ -13254,7 +13272,7 @@
         <v>1178.4480000000001</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471" s="2">
         <v>42036</v>
       </c>
@@ -13272,7 +13290,7 @@
         <v>1285.7719999999999</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A472" s="2">
         <v>42064</v>
       </c>
@@ -13290,7 +13308,7 @@
         <v>1580.393</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A473" s="2">
         <v>42095</v>
       </c>
@@ -13308,7 +13326,7 @@
         <v>1480.4269999999999</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A474" s="2">
         <v>42125</v>
       </c>
@@ -13326,7 +13344,7 @@
         <v>1669.6610000000001</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A475" s="2">
         <v>42156</v>
       </c>
@@ -13344,7 +13362,7 @@
         <v>1519.7339999999999</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476" s="2">
         <v>42186</v>
       </c>
@@ -13362,7 +13380,7 @@
         <v>1547.741</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477" s="2">
         <v>42217</v>
       </c>
@@ -13380,7 +13398,7 @@
         <v>1599.3320000000001</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" s="2">
         <v>42248</v>
       </c>
@@ -13398,7 +13416,7 @@
         <v>1476.009</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" s="2">
         <v>42278</v>
       </c>
@@ -13416,7 +13434,7 @@
         <v>1487.5509999999999</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" s="2">
         <v>42309</v>
       </c>
@@ -13434,7 +13452,7 @@
         <v>1359.864</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" s="2">
         <v>42339</v>
       </c>
@@ -13452,7 +13470,7 @@
         <v>1672.3920000000001</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" s="2">
         <v>42370</v>
       </c>
@@ -13470,7 +13488,7 @@
         <v>1189.3</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" s="2">
         <v>42401</v>
       </c>
@@ -13488,7 +13506,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A484" s="2">
         <v>42430</v>
       </c>
@@ -13506,7 +13524,7 @@
         <v>1615.066</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A485" s="2">
         <v>42461</v>
       </c>
@@ -13524,7 +13542,7 @@
         <v>1525.1659999999999</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A486" s="2">
         <v>42491</v>
       </c>
@@ -13542,7 +13560,7 @@
         <v>1553.604</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A487" s="2">
         <v>42522</v>
       </c>
@@ -13560,7 +13578,7 @@
         <v>1549.8009999999999</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A488" s="2">
         <v>42552</v>
       </c>
@@ -13578,7 +13596,7 @@
         <v>1547.6289999999999</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A489" s="2">
         <v>42583</v>
       </c>
@@ -13596,7 +13614,7 @@
         <v>1540.748</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A490" s="2">
         <v>42614</v>
       </c>
@@ -13614,7 +13632,7 @@
         <v>1463.25</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A491" s="2">
         <v>42644</v>
       </c>
@@ -13632,7 +13650,7 @@
         <v>1398.3610000000001</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A492" s="2">
         <v>42675</v>
       </c>
@@ -13650,7 +13668,7 @@
         <v>1400.7550000000001</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A493" s="2">
         <v>42705</v>
       </c>
@@ -13668,7 +13686,7 @@
         <v>1719.627</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A494" s="2">
         <v>42736</v>
       </c>
@@ -13686,7 +13704,7 @@
         <v>1165.212</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A495" s="2">
         <v>42767</v>
       </c>
@@ -13704,7 +13722,7 @@
         <v>1353.163</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A496" s="2">
         <v>42795</v>
       </c>
@@ -13722,7 +13740,7 @@
         <v>1583.9860000000001</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A497" s="2">
         <v>42826</v>
       </c>
@@ -13740,7 +13758,7 @@
         <v>1450.982</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A498" s="2">
         <v>42856</v>
       </c>
@@ -13758,7 +13776,7 @@
         <v>1545.127</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A499" s="2">
         <v>42887</v>
       </c>
@@ -13776,7 +13794,7 @@
         <v>1503.7080000000001</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A500" s="2">
         <v>42917</v>
       </c>
@@ -13794,7 +13812,7 @@
         <v>1442.0740000000001</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A501" s="2">
         <v>42948</v>
       </c>
@@ -13812,7 +13830,7 @@
         <v>1513.174</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A502" s="2">
         <v>42979</v>
       </c>
@@ -13830,7 +13848,7 @@
         <v>1554.2529999999999</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A503" s="2">
         <v>43009</v>
       </c>
@@ -13848,7 +13866,7 @@
         <v>1386.79</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A504" s="2">
         <v>43040</v>
       </c>
@@ -13866,7 +13884,7 @@
         <v>1425.6690000000001</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A505" s="2">
         <v>43070</v>
       </c>
@@ -13884,7 +13902,7 @@
         <v>1640.989</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A506" s="2">
         <v>43101</v>
       </c>
@@ -13902,7 +13920,7 @@
         <v>1182.6120000000001</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A507" s="2">
         <v>43132</v>
       </c>
@@ -13920,7 +13938,7 @@
         <v>1329.0709999999999</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A508" s="2">
         <v>43160</v>
       </c>
@@ -13938,7 +13956,7 @@
         <v>1688.4939999999999</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A509" s="2">
         <v>43191</v>
       </c>
@@ -13956,7 +13974,7 @@
         <v>1392.164</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A510" s="2">
         <v>43221</v>
       </c>
@@ -13974,7 +13992,7 @@
         <v>1627.509</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A511" s="2">
         <v>43252</v>
       </c>
@@ -13992,7 +14010,7 @@
         <v>1587.643</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A512" s="2">
         <v>43282</v>
       </c>
@@ -14010,7 +14028,7 @@
         <v>1404.0409999999999</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A513" s="2">
         <v>43313</v>
       </c>
@@ -14028,7 +14046,7 @@
         <v>1528.37</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A514" s="2">
         <v>43344</v>
       </c>
@@ -14046,7 +14064,7 @@
         <v>1475.854</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A515" s="2">
         <v>43374</v>
       </c>
@@ -14079,7 +14097,7 @@
         <v>1406.915</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A516" s="2">
         <v>43405</v>
       </c>
@@ -14097,7 +14115,7 @@
         <v>1423.0540000000001</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A517" s="2">
         <v>43435</v>
       </c>
@@ -14115,7 +14133,7 @@
         <v>1667.077</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A518" s="2">
         <v>43466</v>
       </c>
@@ -14133,7 +14151,7 @@
         <v>1172.0039999999999</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A519" s="2">
         <v>43497</v>
       </c>
@@ -14151,7 +14169,7 @@
         <v>1288.921</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A520" s="2">
         <v>43525</v>
       </c>
@@ -14169,7 +14187,7 @@
         <v>1643.423</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A521" s="2">
         <v>43556</v>
       </c>
@@ -14187,7 +14205,7 @@
         <v>1373.3789999999999</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A522" s="2">
         <v>43586</v>
       </c>
@@ -14205,7 +14223,7 @@
         <v>1628.7570000000001</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A523" s="2">
         <v>43617</v>
       </c>
@@ -14223,7 +14241,7 @@
         <v>1555.4929999999999</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A524" s="2">
         <v>43647</v>
       </c>
@@ -14241,7 +14259,7 @@
         <v>1444.4469999999999</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A525" s="2">
         <v>43678</v>
       </c>
@@ -14259,7 +14277,7 @@
         <v>1685.9490000000001</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A526" s="2">
         <v>43709</v>
       </c>
@@ -14277,7 +14295,7 @@
         <v>1316.202</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A527" s="2">
         <v>43739</v>
       </c>
@@ -14295,7 +14313,7 @@
         <v>1381.028</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A528" s="2">
         <v>43770</v>
       </c>
@@ -14313,7 +14331,7 @@
         <v>1439.3219999999999</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A529" s="2">
         <v>43800</v>
       </c>
@@ -14331,7 +14349,7 @@
         <v>1559.229</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A530" s="2">
         <v>43831</v>
       </c>
@@ -14349,7 +14367,7 @@
         <v>1168.4570000000001</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A531" s="2">
         <v>43862</v>
       </c>
@@ -14367,7 +14385,7 @@
         <v>1383.7139999999999</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A532" s="2">
         <v>43891</v>
       </c>
@@ -14385,7 +14403,7 @@
         <v>1023.317</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A533" s="2">
         <v>43922</v>
       </c>
@@ -14403,7 +14421,7 @@
         <v>743.27599999999995</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A534" s="2">
         <v>43952</v>
       </c>
@@ -14421,7 +14439,7 @@
         <v>1142.7049999999999</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A535" s="2">
         <v>43983</v>
       </c>
@@ -14439,7 +14457,7 @@
         <v>1131.3900000000001</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A536" s="2">
         <v>44013</v>
       </c>
@@ -14457,7 +14475,7 @@
         <v>1268.4549999999999</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A537" s="2">
         <v>44044</v>
       </c>
@@ -14475,7 +14493,7 @@
         <v>1354.3969999999999</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A538" s="2">
         <v>44075</v>
       </c>
@@ -14493,7 +14511,7 @@
         <v>1379.6759999999999</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A539" s="2">
         <v>44105</v>
       </c>
@@ -14511,7 +14529,7 @@
         <v>1399.3050000000001</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A540" s="2">
         <v>44136</v>
       </c>
@@ -14529,7 +14547,7 @@
         <v>1235.258</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A541" s="2">
         <v>44166</v>
       </c>
@@ -14547,7 +14565,7 @@
         <v>1651.4059999999999</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A542" s="2">
         <v>44197</v>
       </c>
@@ -14565,7 +14583,7 @@
         <v>1141.7090000000001</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A543" s="2">
         <v>44228</v>
       </c>
@@ -14583,7 +14601,7 @@
         <v>1226.7139999999999</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A544" s="2">
         <v>44256</v>
       </c>
@@ -14601,7 +14619,7 @@
         <v>1642.749</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A545" s="2">
         <v>44287</v>
       </c>
@@ -14619,7 +14637,7 @@
         <v>1557.152</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A546" s="2">
         <v>44317</v>
       </c>
@@ -14637,7 +14655,7 @@
         <v>1608.6279999999999</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A547" s="2">
         <v>44348</v>
       </c>
@@ -14655,7 +14673,7 @@
         <v>1342.999</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A548" s="2">
         <v>44378</v>
       </c>
@@ -14673,7 +14691,7 @@
         <v>1316.6969999999999</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A549" s="2">
         <v>44409</v>
       </c>
@@ -14691,7 +14709,7 @@
         <v>1128.9649999999999</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A550" s="2">
         <v>44440</v>
       </c>
@@ -14709,7 +14727,7 @@
         <v>1052.9649999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A551" s="2">
         <v>44470</v>
       </c>
@@ -14727,7 +14745,7 @@
         <v>1089.348</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A552" s="2">
         <v>44501</v>
       </c>
@@ -14745,7 +14763,7 @@
         <v>1049.604</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A553" s="2">
         <v>44531</v>
       </c>
@@ -14763,7 +14781,7 @@
         <v>1250.9849999999999</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A554" s="2">
         <v>44562</v>
       </c>
@@ -14781,7 +14799,7 @@
         <v>1022.3339999999999</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A555" s="2">
         <v>44593</v>
       </c>
@@ -14799,7 +14817,7 @@
         <v>1077.808</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A556" s="2">
         <v>44621</v>
       </c>
@@ -14817,7 +14835,7 @@
         <v>1299.2260000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A557" s="2">
         <v>44652</v>
       </c>
@@ -14835,7 +14853,7 @@
         <v>1271.8879999999999</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A558" s="2">
         <v>44682</v>
       </c>
@@ -14853,7 +14871,7 @@
         <v>1145.623</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A559" s="2">
         <v>44713</v>
       </c>
@@ -14871,7 +14889,7 @@
         <v>1184.4369999999999</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A560" s="2">
         <v>44743</v>
       </c>
@@ -14889,7 +14907,7 @@
         <v>1164.691</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A561" s="2">
         <v>44774</v>
       </c>
@@ -14907,7 +14925,7 @@
         <v>1178.066</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A562" s="2">
         <v>44805</v>
       </c>
@@ -14925,7 +14943,7 @@
         <v>1166.0150000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A563" s="2">
         <v>44835</v>
       </c>
@@ -14943,7 +14961,7 @@
         <v>1224.6790000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A564" s="2">
         <v>44866</v>
       </c>
@@ -14961,7 +14979,7 @@
         <v>1176.556</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A565" s="2">
         <v>44896</v>
       </c>
@@ -14979,7 +14997,7 @@
         <v>1319.001</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A566" s="2">
         <v>44927</v>
       </c>
@@ -14997,7 +15015,7 @@
         <v>1083.376</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A567" s="2">
         <v>44958</v>
       </c>
@@ -15015,7 +15033,7 @@
         <v>1175.6279999999999</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A568" s="2">
         <v>44986</v>
       </c>
@@ -15033,7 +15051,7 @@
         <v>1419.662</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A569" s="2">
         <v>45017</v>
       </c>
@@ -15051,7 +15069,7 @@
         <v>1399.712</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A570" s="2">
         <v>45047</v>
       </c>
@@ -15069,7 +15087,7 @@
         <v>1409.6010000000001</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A571" s="2">
         <v>45078</v>
       </c>
@@ -15087,7 +15105,7 @@
         <v>1415.002</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A572" s="2">
         <v>45108</v>
       </c>
@@ -15105,7 +15123,7 @@
         <v>1339.904</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A573" s="2">
         <v>45139</v>
       </c>
@@ -15123,7 +15141,7 @@
         <v>1364.9680000000001</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A574" s="2">
         <v>45170</v>
       </c>
@@ -15141,7 +15159,7 @@
         <v>1383.3810000000001</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A575" s="2">
         <v>45200</v>
       </c>
@@ -15159,7 +15177,7 @@
         <v>1239.4970000000001</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A576" s="2">
         <v>45231</v>
       </c>
@@ -15177,7 +15195,7 @@
         <v>1273.4880000000001</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A577" s="2">
         <v>45261</v>
       </c>
@@ -15195,7 +15213,7 @@
         <v>1505.049</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A578" s="2">
         <v>45292</v>
       </c>
@@ -15213,7 +15231,7 @@
         <v>1106.8130000000001</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A579" s="2">
         <v>45323</v>
       </c>
@@ -15221,7 +15239,7 @@
         <v>45380</v>
       </c>
       <c r="D579" s="3" t="str">
-        <f t="shared" ref="D579:D606" si="9">IF(
+        <f t="shared" ref="D579:D607" si="9">IF(
  AND(
   B579 &gt;= IF(
          YEAR(B579)&gt;=2007,
@@ -15246,7 +15264,7 @@
         <v>1265.0440000000001</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A580" s="2">
         <v>45352</v>
       </c>
@@ -15264,7 +15282,7 @@
         <v>1471.038</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A581" s="2">
         <v>45383</v>
       </c>
@@ -15282,7 +15300,7 @@
         <v>1359.2380000000001</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A582" s="2">
         <v>45413</v>
       </c>
@@ -15300,7 +15318,7 @@
         <v>1472.636</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A583" s="2">
         <v>45444</v>
       </c>
@@ -15318,7 +15336,7 @@
         <v>1348.41</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A584" s="2">
         <v>45474</v>
       </c>
@@ -15336,7 +15354,7 @@
         <v>1328.9349999999999</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A585" s="2">
         <v>45505</v>
       </c>
@@ -15354,7 +15372,7 @@
         <v>1457.1590000000001</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A586" s="2">
         <v>45536</v>
       </c>
@@ -15372,7 +15390,7 @@
         <v>1213.4359999999999</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A587" s="2">
         <v>45566</v>
       </c>
@@ -15390,7 +15408,7 @@
         <v>1368.0309999999999</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A588" s="2">
         <v>45597</v>
       </c>
@@ -15408,7 +15426,7 @@
         <v>1403.806</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A589" s="2">
         <v>45627</v>
       </c>
@@ -15426,7 +15444,7 @@
         <v>1538.9259999999999</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A590" s="2">
         <v>45658</v>
       </c>
@@ -15444,7 +15462,7 @@
         <v>1141.587</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A591" s="2">
         <v>45689</v>
       </c>
@@ -15462,7 +15480,7 @@
         <v>1246.616</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A592" s="2">
         <v>45717</v>
       </c>
@@ -15480,7 +15498,7 @@
         <v>1631.6369999999999</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A593" s="2">
         <v>45748</v>
       </c>
@@ -15498,7 +15516,7 @@
         <v>1500.4390000000001</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A594" s="2">
         <v>45778</v>
       </c>
@@ -15516,7 +15534,7 @@
         <v>1498.3620000000001</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A595" s="2">
         <v>45809</v>
       </c>
@@ -15534,7 +15552,7 @@
         <v>1310.6489999999999</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A596" s="2">
         <v>45839</v>
       </c>
@@ -15552,7 +15570,7 @@
         <v>1425.72</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A597" s="2">
         <v>45870</v>
       </c>
@@ -15570,7 +15588,7 @@
         <v>1500.357</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A598" s="2">
         <v>45901</v>
       </c>
@@ -15588,7 +15606,7 @@
         <v>1299.164</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A599" s="2">
         <v>45931</v>
       </c>
@@ -15606,7 +15624,7 @@
         <v>1316.87</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A600" s="2">
         <v>45962</v>
       </c>
@@ -15624,7 +15642,7 @@
         <v>1305.1790000000001</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A601" s="2">
         <v>45992</v>
       </c>
@@ -15642,7 +15660,7 @@
         <v>1498.9079999999999</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A602" s="2">
         <v>46023</v>
       </c>
@@ -15660,7 +15678,7 @@
         <v>1115.819</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A603" s="2">
         <v>46054</v>
       </c>
@@ -15678,7 +15696,7 @@
         <v>1205.383</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A604" s="2">
         <v>46082</v>
       </c>
@@ -15696,7 +15714,7 @@
         <v>1420.6210000000001</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A605" s="2">
         <v>46113</v>
       </c>
@@ -15714,7 +15732,7 @@
         <v>1401.19</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A606" s="2">
         <v>46143</v>
       </c>
@@ -15733,6 +15751,27 @@
       </c>
       <c r="F606" s="7">
         <v>1499.3019999999999</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A607" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B607" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C607" s="5">
+        <v>5.486111111111111E-2</v>
+      </c>
+      <c r="D607" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E607" s="1">
+        <v>16.949000000000002</v>
+      </c>
+      <c r="F607" s="7">
+        <v>1400.328</v>
       </c>
     </row>
   </sheetData>
@@ -15743,13 +15782,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBF91B7-B4B2-4C99-8837-D8989C04A2D6}">
   <dimension ref="B2:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
@@ -15760,23 +15799,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
@@ -15788,6 +15827,7 @@
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{35AAA25A-BA60-4389-8324-051E0DAF4838}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{9714618A-2270-2743-8D4D-84AADC72C466}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{9ED16313-083A-4815-A44D-DFCAF501DEE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
